--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramakrishna.tummala\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18395B1C-30CC-4D18-BED3-6A2464CAF047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52440EC-12A8-4585-A51A-7C834A44DB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="116">
   <si>
     <t>Name</t>
   </si>
@@ -406,6 +406,18 @@
   </si>
   <si>
     <t>Data Source={0};Initial Catalog={1};User ID={2};Password={3};Encrypt=False</t>
+  </si>
+  <si>
+    <t>ArbitratorRegistryurl</t>
+  </si>
+  <si>
+    <t>https://ptrp.app.cpa.state.tx.us/home/arbitratorregistry</t>
+  </si>
+  <si>
+    <t>ArbitratorRegistrySheetName</t>
+  </si>
+  <si>
+    <t>Export</t>
   </si>
 </sst>
 </file>
@@ -513,7 +525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -540,6 +552,7 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z947"/>
+  <dimension ref="A1:Z949"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.81640625" bestFit="1" customWidth="1"/>
@@ -1086,116 +1099,116 @@
       </c>
       <c r="C21" s="7"/>
     </row>
-    <row r="22" spans="1:3" ht="21">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:3" ht="14.5">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:3" ht="14.5">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" ht="21">
+      <c r="A24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B25" s="15" t="s">
         <v>108</v>
-      </c>
-      <c r="C23" s="6"/>
-    </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
         <v>110</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="6"/>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" s="9" t="s">
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B30" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1">
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" spans="1:3" ht="21">
-      <c r="A30" s="8" t="s">
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1">
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:3" ht="21">
+      <c r="A32" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2">
-        <v>3</v>
-      </c>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B32" s="6"/>
       <c r="C32" s="6"/>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>45</v>
+        <v>4</v>
+      </c>
+      <c r="B33" s="2">
+        <v>3</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>45</v>
@@ -1204,7 +1217,7 @@
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>24</v>
@@ -1213,236 +1226,252 @@
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C37" s="6"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="2">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C39" s="6"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
       </c>
       <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C44" s="6"/>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C45" s="6"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C46" s="6"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="2">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="C47" s="6"/>
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="2">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6"/>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="3" t="b">
+      <c r="B51" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="51" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A51" s="1" t="s">
+      <c r="C51" s="6"/>
+    </row>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="53" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1">
       <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A56" t="s">
         <v>57</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B56" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="56" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="57" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A57" s="10" t="s">
+    <row r="57" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A59" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A58" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A59" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1">
       <c r="A64" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A65" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A66" t="s">
         <v>90</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B66" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="67" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="68" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="69" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="70" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="71" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="72" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="73" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="74" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="75" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="76" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="77" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="78" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="79" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="80" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="81" ht="14.25" customHeight="1"/>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -2310,6 +2339,8 @@
     <row r="945" ht="14.25" customHeight="1"/>
     <row r="946" ht="14.25" customHeight="1"/>
     <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
